--- a/artfynd/A 7585-2023 artfynd.xlsx
+++ b/artfynd/A 7585-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 7585-2023 artfynd.xlsx
+++ b/artfynd/A 7585-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>57075646</v>
       </c>
       <c r="B2" t="n">
-        <v>93132</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96426</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570123.9750288331</v>
+        <v>570124</v>
       </c>
       <c r="R2" t="n">
-        <v>6536864.380951291</v>
+        <v>6536864</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -751,19 +746,9 @@
           <t>2016-02-24</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2016-02-24</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,16 +778,11 @@
         <v>57075633</v>
       </c>
       <c r="B3" t="n">
-        <v>57007</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -841,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570123.9750288331</v>
+        <v>570124</v>
       </c>
       <c r="R3" t="n">
-        <v>6536864.380951291</v>
+        <v>6536864</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -874,19 +854,9 @@
           <t>2016-02-24</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-02-24</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,15 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>57075642</v>
+        <v>57075632</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58636</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,37 +894,45 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djulönäs SV, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>570123.9750288331</v>
+        <v>570124</v>
       </c>
       <c r="R4" t="n">
-        <v>6536864.380951291</v>
+        <v>6536864</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -989,19 +962,9 @@
           <t>2016-02-24</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-02-24</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,6 +988,106 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>57075642</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Djulönäs SV, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>570124</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6536864</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Stora Malm</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2016-02-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2016-02-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Lernefalk</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7585-2023 artfynd.xlsx
+++ b/artfynd/A 7585-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -772,6 +777,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57075646</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -880,6 +890,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57075633</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,6 +1003,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57075632</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,8 +1108,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57075642</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>